--- a/salidas/empresas/LOW.xlsx
+++ b/salidas/empresas/LOW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>23.92022323608398</v>
+        <v>23.92023277282715</v>
       </c>
       <c r="C3" t="n">
         <v>34.09000015258789</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>22.60808944702148</v>
+        <v>22.60809516906738</v>
       </c>
       <c r="C4" t="n">
         <v>32.22000122070312</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>22.14114189147949</v>
+        <v>22.14113235473633</v>
       </c>
       <c r="C5" t="n">
         <v>31.52499961853027</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>21.87073516845703</v>
+        <v>21.87073707580566</v>
       </c>
       <c r="C6" t="n">
         <v>31.13999938964844</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>21.30535697937012</v>
+        <v>21.30536651611328</v>
       </c>
       <c r="C7" t="n">
         <v>30.33499908447266</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>19.94713973999023</v>
+        <v>19.94714736938477</v>
       </c>
       <c r="C8" t="n">
         <v>28.35000038146973</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>19.03948593139648</v>
+        <v>19.03948211669922</v>
       </c>
       <c r="C9" t="n">
         <v>27.05999946594238</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>19.74309158325195</v>
+        <v>19.74309349060059</v>
       </c>
       <c r="C10" t="n">
         <v>28.05999946594238</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>21.24135589599609</v>
+        <v>21.24135208129883</v>
       </c>
       <c r="C11" t="n">
         <v>30.13999938964844</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>21.25544738769531</v>
+        <v>21.25544929504395</v>
       </c>
       <c r="C12" t="n">
         <v>30.15999984741211</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>21.95315742492676</v>
+        <v>21.95315170288086</v>
       </c>
       <c r="C13" t="n">
         <v>31.14999961853027</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>23.79295349121094</v>
+        <v>23.79294967651367</v>
       </c>
       <c r="C14" t="n">
         <v>33.70999908447266</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>22.97420310974121</v>
+        <v>22.97421646118164</v>
       </c>
       <c r="C15" t="n">
         <v>32.54999923706055</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>22.22605133056641</v>
+        <v>22.22603988647461</v>
       </c>
       <c r="C16" t="n">
         <v>31.48999977111816</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>21.60356903076172</v>
+        <v>21.60357093811035</v>
       </c>
       <c r="C17" t="n">
         <v>30.55999946594238</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>23.20120620727539</v>
+        <v>23.20120811462402</v>
       </c>
       <c r="C18" t="n">
         <v>32.81999969482422</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>19.85411262512207</v>
+        <v>19.85410690307617</v>
       </c>
       <c r="C20" t="n">
         <v>28.01000022888184</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>19.86119651794434</v>
+        <v>19.86118698120117</v>
       </c>
       <c r="C22" t="n">
         <v>28.02000045776367</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>19.11532783508301</v>
+        <v>19.11533355712891</v>
       </c>
       <c r="C23" t="n">
         <v>26.88999938964844</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>18.86098289489746</v>
+        <v>18.8609733581543</v>
       </c>
       <c r="C26" t="n">
         <v>26.43000030517578</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>17.10546875</v>
+        <v>17.10547065734863</v>
       </c>
       <c r="C27" t="n">
         <v>23.96999931335449</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>16.37045288085938</v>
+        <v>16.37043571472168</v>
       </c>
       <c r="C28" t="n">
         <v>22.94000053405762</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>18.03571319580078</v>
+        <v>18.03570556640625</v>
       </c>
       <c r="C29" t="n">
         <v>25.19000053405762</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>17.18368911743164</v>
+        <v>17.18369293212891</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>14.85673046112061</v>
+        <v>14.85672760009766</v>
       </c>
       <c r="C31" t="n">
         <v>20.75</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>14.61682224273682</v>
+        <v>14.61682415008545</v>
       </c>
       <c r="C32" t="n">
         <v>20.31999969482422</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>17.72432899475098</v>
+        <v>17.72433662414551</v>
       </c>
       <c r="C33" t="n">
         <v>24.63999938964844</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>15.67902374267578</v>
+        <v>15.6790189743042</v>
       </c>
       <c r="C35" t="n">
         <v>21.70000076293945</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>14.92757701873779</v>
+        <v>14.92758464813232</v>
       </c>
       <c r="C36" t="n">
         <v>20.65999984741211</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>15.54896926879883</v>
+        <v>15.54896545410156</v>
       </c>
       <c r="C37" t="n">
         <v>21.52000045776367</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.25622940063477</v>
+        <v>13.25622844696045</v>
       </c>
       <c r="C38" t="n">
         <v>18.27000045776367</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>11.49308204650879</v>
+        <v>11.49308681488037</v>
       </c>
       <c r="C39" t="n">
         <v>15.84000015258789</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>15.66698455810547</v>
+        <v>15.66698932647705</v>
       </c>
       <c r="C41" t="n">
         <v>21.5</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>13.85253143310547</v>
+        <v>13.85252952575684</v>
       </c>
       <c r="C42" t="n">
         <v>19.01000022888184</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.14400863647461</v>
+        <v>14.14401531219482</v>
       </c>
       <c r="C43" t="n">
         <v>19.40999984741211</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>16.44214630126953</v>
+        <v>16.44215202331543</v>
       </c>
       <c r="C44" t="n">
         <v>22.45999908447266</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>15.73937320709229</v>
+        <v>15.73937511444092</v>
       </c>
       <c r="C45" t="n">
         <v>21.5</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>15.32941722869873</v>
+        <v>15.32941246032715</v>
       </c>
       <c r="C46" t="n">
         <v>20.94000053405762</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>14.38684844970703</v>
+        <v>14.38685131072998</v>
       </c>
       <c r="C47" t="n">
         <v>19.56999969482422</v>
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>16.03358268737793</v>
+        <v>16.03358459472656</v>
       </c>
       <c r="C48" t="n">
         <v>21.80999946594238</v>
@@ -1393,11 +1405,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>17.19512176513672</v>
+        <v>17.19511985778809</v>
       </c>
       <c r="C49" t="n">
         <v>23.38999938964844</v>
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>15.97797012329102</v>
+        <v>15.97796440124512</v>
       </c>
       <c r="C50" t="n">
         <v>21.64999961853027</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>17.4982795715332</v>
+        <v>17.4982738494873</v>
       </c>
       <c r="C51" t="n">
         <v>23.70999908447266</v>
@@ -1468,7 +1480,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1493,7 +1505,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>18.32855033874512</v>
+        <v>18.32855415344238</v>
       </c>
       <c r="C54" t="n">
         <v>24.75</v>
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>15.12198066711426</v>
+        <v>15.12197780609131</v>
       </c>
       <c r="C55" t="n">
         <v>20.42000007629395</v>
@@ -1568,11 +1580,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>15.4437255859375</v>
+        <v>15.44372367858887</v>
       </c>
       <c r="C56" t="n">
         <v>20.73999977111816</v>
@@ -1593,11 +1605,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>15.10119915008545</v>
+        <v>15.10120010375977</v>
       </c>
       <c r="C57" t="n">
         <v>20.28000068664551</v>
@@ -1618,11 +1630,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>16.5979061126709</v>
+        <v>16.5979118347168</v>
       </c>
       <c r="C58" t="n">
         <v>22.29000091552734</v>
@@ -1643,11 +1655,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>15.97200584411621</v>
+        <v>15.97199821472168</v>
       </c>
       <c r="C59" t="n">
         <v>21.34000015258789</v>
@@ -1668,7 +1680,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1693,11 +1705,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>18.77121543884277</v>
+        <v>18.77121925354004</v>
       </c>
       <c r="C61" t="n">
         <v>25.07999992370605</v>
@@ -1718,11 +1730,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>18.64518165588379</v>
+        <v>18.64518737792969</v>
       </c>
       <c r="C62" t="n">
         <v>24.79999923706055</v>
@@ -1743,11 +1755,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>19.6751823425293</v>
+        <v>19.67519187927246</v>
       </c>
       <c r="C63" t="n">
         <v>26.17000007629395</v>
@@ -1768,11 +1780,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>19.87066459655762</v>
+        <v>19.87066078186035</v>
       </c>
       <c r="C64" t="n">
         <v>26.43000030517578</v>
@@ -1797,11 +1809,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>19.81591415405273</v>
+        <v>19.8159122467041</v>
       </c>
       <c r="C65" t="n">
         <v>26.25</v>
@@ -1826,11 +1838,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>18.22309303283691</v>
+        <v>18.22309112548828</v>
       </c>
       <c r="C66" t="n">
         <v>24.13999938964844</v>
@@ -1855,11 +1867,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>17.59653472900391</v>
+        <v>17.59653091430664</v>
       </c>
       <c r="C67" t="n">
         <v>23.30999946594238</v>
@@ -1884,11 +1896,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>16.39095115661621</v>
+        <v>16.39094543457031</v>
       </c>
       <c r="C68" t="n">
         <v>21.57999992370605</v>
@@ -1913,11 +1925,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>15.13770771026611</v>
+        <v>15.13770484924316</v>
       </c>
       <c r="C69" t="n">
         <v>19.93000030517578</v>
@@ -1942,11 +1954,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>14.6895694732666</v>
+        <v>14.68957710266113</v>
       </c>
       <c r="C70" t="n">
         <v>19.34000015258789</v>
@@ -1971,11 +1983,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>16.0731201171875</v>
+        <v>16.07311630249023</v>
       </c>
       <c r="C71" t="n">
         <v>21.02000045776367</v>
@@ -2000,7 +2012,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2029,11 +2041,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>19.40702629089355</v>
+        <v>19.40702247619629</v>
       </c>
       <c r="C73" t="n">
         <v>25.3799991607666</v>
@@ -2058,7 +2070,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2087,7 +2099,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2116,11 +2128,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>24.12227058410645</v>
+        <v>24.12227439880371</v>
       </c>
       <c r="C76" t="n">
         <v>31.3799991607666</v>
@@ -2145,11 +2157,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>24.2989387512207</v>
+        <v>24.29894638061523</v>
       </c>
       <c r="C77" t="n">
         <v>31.46999931335449</v>
@@ -2174,11 +2186,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>20.63131523132324</v>
+        <v>20.63132667541504</v>
       </c>
       <c r="C78" t="n">
         <v>26.71999931335449</v>
@@ -2203,11 +2215,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>21.95938491821289</v>
+        <v>21.95938873291016</v>
       </c>
       <c r="C79" t="n">
         <v>28.44000053405762</v>
@@ -2232,11 +2244,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>19.71123886108398</v>
+        <v>19.71124267578125</v>
       </c>
       <c r="C80" t="n">
         <v>25.3700008392334</v>
@@ -2261,11 +2273,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>22.12755393981934</v>
+        <v>22.1275463104248</v>
       </c>
       <c r="C81" t="n">
         <v>28.47999954223633</v>
@@ -2290,11 +2302,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>23.49498176574707</v>
+        <v>23.4949836730957</v>
       </c>
       <c r="C82" t="n">
         <v>30.23999977111816</v>
@@ -2319,11 +2331,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>25.28158760070801</v>
+        <v>25.28158950805664</v>
       </c>
       <c r="C83" t="n">
         <v>32.38000106811523</v>
@@ -2348,11 +2360,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>28.17827033996582</v>
+        <v>28.17827224731445</v>
       </c>
       <c r="C84" t="n">
         <v>36.09000015258789</v>
@@ -2377,11 +2389,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>27.73323249816895</v>
+        <v>27.73323440551758</v>
       </c>
       <c r="C85" t="n">
         <v>35.52000045776367</v>
@@ -2406,7 +2418,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2435,7 +2447,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2464,7 +2476,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2493,11 +2505,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>30.25475883483887</v>
+        <v>30.2547435760498</v>
       </c>
       <c r="C89" t="n">
         <v>38.41999816894531</v>
@@ -2522,11 +2534,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>33.16054916381836</v>
+        <v>33.16053771972656</v>
       </c>
       <c r="C90" t="n">
         <v>42.11000061035156</v>
@@ -2551,11 +2563,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>32.20767974853516</v>
+        <v>32.20770645141602</v>
       </c>
       <c r="C91" t="n">
         <v>40.90000152587891</v>
@@ -2580,11 +2592,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>35.2489128112793</v>
+        <v>35.24890899658203</v>
       </c>
       <c r="C92" t="n">
         <v>44.58000183105469</v>
@@ -2609,7 +2621,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2638,11 +2650,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>37.64470291137695</v>
+        <v>37.64470672607422</v>
       </c>
       <c r="C94" t="n">
         <v>47.61000061035156</v>
@@ -2667,11 +2679,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>39.50971221923828</v>
+        <v>39.50970840454102</v>
       </c>
       <c r="C95" t="n">
         <v>49.77999877929688</v>
@@ -2696,11 +2708,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>37.68424987792969</v>
+        <v>37.68421936035156</v>
       </c>
       <c r="C96" t="n">
         <v>47.47999954223633</v>
@@ -2725,7 +2737,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2754,11 +2766,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>36.87751770019531</v>
+        <v>36.87752151489258</v>
       </c>
       <c r="C98" t="n">
         <v>46.29000091552734</v>
@@ -2783,11 +2795,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>39.85703659057617</v>
+        <v>39.85703277587891</v>
       </c>
       <c r="C99" t="n">
         <v>50.02999877929688</v>
@@ -2812,7 +2824,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2841,7 +2853,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2870,11 +2882,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>37.65170288085938</v>
+        <v>37.65171051025391</v>
       </c>
       <c r="C102" t="n">
         <v>47.08000183105469</v>
@@ -2899,11 +2911,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>38.37945938110352</v>
+        <v>38.37946701049805</v>
       </c>
       <c r="C103" t="n">
         <v>47.9900016784668</v>
@@ -2928,7 +2940,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2957,11 +2969,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>42.19728469848633</v>
+        <v>42.19729232788086</v>
       </c>
       <c r="C105" t="n">
         <v>52.5099983215332</v>
@@ -2986,11 +2998,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>42.52675247192383</v>
+        <v>42.52675628662109</v>
       </c>
       <c r="C106" t="n">
         <v>52.91999816894531</v>
@@ -3015,11 +3027,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>46.16841888427734</v>
+        <v>46.16841506958008</v>
       </c>
       <c r="C107" t="n">
         <v>57.20000076293945</v>
@@ -3044,7 +3056,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3073,11 +3085,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>55.53124618530273</v>
+        <v>55.5312385559082</v>
       </c>
       <c r="C109" t="n">
         <v>68.80000305175781</v>
@@ -3102,11 +3114,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>54.8820686340332</v>
+        <v>54.88206100463867</v>
       </c>
       <c r="C110" t="n">
         <v>67.76000213623047</v>
@@ -3131,11 +3143,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>60.00904083251953</v>
+        <v>60.00902938842773</v>
       </c>
       <c r="C111" t="n">
         <v>74.08999633789062</v>
@@ -3160,11 +3172,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>60.25199127197266</v>
+        <v>60.25200653076172</v>
       </c>
       <c r="C112" t="n">
         <v>74.38999938964844</v>
@@ -3189,11 +3201,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>55.95036697387695</v>
+        <v>55.95038986206055</v>
       </c>
       <c r="C113" t="n">
         <v>68.86000061035156</v>
@@ -3218,11 +3230,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>56.86039733886719</v>
+        <v>56.86040115356445</v>
       </c>
       <c r="C114" t="n">
         <v>69.98000335693359</v>
@@ -3247,11 +3259,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>54.41473388671875</v>
+        <v>54.41471099853516</v>
       </c>
       <c r="C115" t="n">
         <v>66.97000122070312</v>
@@ -3276,11 +3288,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>56.59127044677734</v>
+        <v>56.59126663208008</v>
       </c>
       <c r="C116" t="n">
         <v>69.36000061035156</v>
@@ -3305,11 +3317,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>56.43624496459961</v>
+        <v>56.43625640869141</v>
       </c>
       <c r="C117" t="n">
         <v>69.16999816894531</v>
@@ -3334,11 +3346,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>56.23229217529297</v>
+        <v>56.23228073120117</v>
       </c>
       <c r="C118" t="n">
         <v>68.91999816894531</v>
@@ -3363,11 +3375,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>60.47102355957031</v>
+        <v>60.47101974487305</v>
       </c>
       <c r="C119" t="n">
         <v>73.83000183105469</v>
@@ -3392,11 +3404,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>62.73981475830078</v>
+        <v>62.73983001708984</v>
       </c>
       <c r="C120" t="n">
         <v>76.59999847412109</v>
@@ -3421,11 +3433,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>62.28114318847656</v>
+        <v>62.28113555908203</v>
       </c>
       <c r="C121" t="n">
         <v>76.04000091552734</v>
@@ -3450,11 +3462,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>58.92971801757812</v>
+        <v>58.92971038818359</v>
       </c>
       <c r="C122" t="n">
         <v>71.66000366210938</v>
@@ -3479,11 +3491,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>55.53337097167969</v>
+        <v>55.53337860107422</v>
       </c>
       <c r="C123" t="n">
         <v>67.52999877929688</v>
@@ -3508,11 +3520,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>62.29309844970703</v>
+        <v>62.2931022644043</v>
       </c>
       <c r="C124" t="n">
         <v>75.75</v>
@@ -3537,11 +3549,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>62.74237442016602</v>
+        <v>62.74238586425781</v>
       </c>
       <c r="C125" t="n">
         <v>76.01999664306641</v>
@@ -3566,11 +3578,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>66.13453674316406</v>
+        <v>66.13451385498047</v>
       </c>
       <c r="C126" t="n">
         <v>80.12999725341797</v>
@@ -3595,11 +3607,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>65.34219360351562</v>
+        <v>65.34220123291016</v>
       </c>
       <c r="C127" t="n">
         <v>79.16999816894531</v>
@@ -3624,11 +3636,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>68.20130157470703</v>
+        <v>68.20127105712891</v>
       </c>
       <c r="C128" t="n">
         <v>82.27999877929688</v>
@@ -3653,7 +3665,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3682,11 +3694,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>59.85432815551758</v>
+        <v>59.85433197021484</v>
       </c>
       <c r="C130" t="n">
         <v>72.20999908447266</v>
@@ -3711,7 +3723,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3740,11 +3752,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>58.76667022705078</v>
+        <v>58.76666641235352</v>
       </c>
       <c r="C132" t="n">
         <v>70.55000305175781</v>
@@ -3769,11 +3781,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>59.24144744873047</v>
+        <v>59.24143981933594</v>
       </c>
       <c r="C133" t="n">
         <v>71.12000274658203</v>
@@ -3798,11 +3810,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>61.17245483398438</v>
+        <v>61.17245864868164</v>
       </c>
       <c r="C134" t="n">
         <v>73.08000183105469</v>
@@ -3827,11 +3839,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>62.25227355957031</v>
+        <v>62.25225830078125</v>
       </c>
       <c r="C135" t="n">
         <v>74.37000274658203</v>
@@ -3856,11 +3868,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>68.81484222412109</v>
+        <v>68.81483459472656</v>
       </c>
       <c r="C136" t="n">
         <v>82.20999908447266</v>
@@ -3885,11 +3897,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>71.34893798828125</v>
+        <v>71.34894561767578</v>
       </c>
       <c r="C137" t="n">
         <v>84.87999725341797</v>
@@ -3914,11 +3926,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>66.21298980712891</v>
+        <v>66.21295928955078</v>
       </c>
       <c r="C138" t="n">
         <v>78.76999664306641</v>
@@ -3943,11 +3955,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>65.17063903808594</v>
+        <v>65.17061614990234</v>
       </c>
       <c r="C139" t="n">
         <v>77.52999877929688</v>
@@ -3972,11 +3984,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>65.42464447021484</v>
+        <v>65.42465209960938</v>
       </c>
       <c r="C140" t="n">
         <v>77.40000152587891</v>
@@ -4001,11 +4013,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>62.45772171020508</v>
+        <v>62.45769882202148</v>
       </c>
       <c r="C141" t="n">
         <v>73.88999938964844</v>
@@ -4030,11 +4042,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>67.57166290283203</v>
+        <v>67.57164764404297</v>
       </c>
       <c r="C142" t="n">
         <v>79.94000244140625</v>
@@ -4059,11 +4071,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>67.92644500732422</v>
+        <v>67.92645263671875</v>
       </c>
       <c r="C143" t="n">
         <v>79.94999694824219</v>
@@ -4088,7 +4100,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4117,11 +4129,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>78.96292877197266</v>
+        <v>78.96292114257812</v>
       </c>
       <c r="C145" t="n">
         <v>92.94000244140625</v>
@@ -4146,11 +4158,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>89.32176971435547</v>
+        <v>89.32175445556641</v>
       </c>
       <c r="C146" t="n">
         <v>104.7300033569336</v>
@@ -4175,11 +4187,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>76.40921020507812</v>
+        <v>76.40918731689453</v>
       </c>
       <c r="C147" t="n">
         <v>89.58999633789062</v>
@@ -4204,11 +4216,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>74.83989715576172</v>
+        <v>74.83988952636719</v>
       </c>
       <c r="C148" t="n">
         <v>87.75</v>
@@ -4233,11 +4245,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>70.64599609375</v>
+        <v>70.64600372314453</v>
       </c>
       <c r="C149" t="n">
         <v>82.43000030517578</v>
@@ -4262,11 +4274,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>81.42759704589844</v>
+        <v>81.42758178710938</v>
       </c>
       <c r="C150" t="n">
         <v>95.01000213623047</v>
@@ -4291,7 +4303,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4320,11 +4332,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>85.54448699951172</v>
+        <v>85.54447174072266</v>
       </c>
       <c r="C152" t="n">
         <v>99.33999633789062</v>
@@ -4349,11 +4361,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>93.64769744873047</v>
+        <v>93.64768218994141</v>
       </c>
       <c r="C153" t="n">
         <v>108.75</v>
@@ -4378,11 +4390,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>98.87474822998047</v>
+        <v>98.87473297119141</v>
       </c>
       <c r="C154" t="n">
         <v>114.8199996948242</v>
@@ -4407,11 +4419,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>82.39862060546875</v>
+        <v>82.39861297607422</v>
       </c>
       <c r="C155" t="n">
         <v>95.22000122070312</v>
@@ -4436,7 +4448,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4465,11 +4477,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>79.92372131347656</v>
+        <v>79.9237060546875</v>
       </c>
       <c r="C157" t="n">
         <v>92.36000061035156</v>
@@ -4494,7 +4506,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4523,11 +4535,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>91.40153503417969</v>
+        <v>91.40150451660156</v>
       </c>
       <c r="C159" t="n">
         <v>105.0899963378906</v>
@@ -4552,11 +4564,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>95.21100616455078</v>
+        <v>95.21102905273438</v>
       </c>
       <c r="C160" t="n">
         <v>109.4700012207031</v>
@@ -4581,11 +4593,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>98.82113647460938</v>
+        <v>98.82115173339844</v>
       </c>
       <c r="C161" t="n">
         <v>113.1399993896484</v>
@@ -4610,11 +4622,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>81.47460174560547</v>
+        <v>81.47461700439453</v>
       </c>
       <c r="C162" t="n">
         <v>93.27999877929688</v>
@@ -4639,11 +4651,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>88.13897705078125</v>
+        <v>88.13895416259766</v>
       </c>
       <c r="C163" t="n">
         <v>100.9100036621094</v>
@@ -4668,11 +4680,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>89.04451751708984</v>
+        <v>89.04453277587891</v>
       </c>
       <c r="C164" t="n">
         <v>101.4000015258789</v>
@@ -4697,11 +4709,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>98.52854919433594</v>
+        <v>98.52857208251953</v>
       </c>
       <c r="C165" t="n">
         <v>112.1999969482422</v>
@@ -4726,11 +4738,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>96.56151580810547</v>
+        <v>96.56150054931641</v>
       </c>
       <c r="C166" t="n">
         <v>109.9599990844727</v>
@@ -4755,11 +4767,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>98.49433898925781</v>
+        <v>98.49434661865234</v>
       </c>
       <c r="C167" t="n">
         <v>111.6100006103516</v>
@@ -4784,11 +4796,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>103.524528503418</v>
+        <v>103.5245208740234</v>
       </c>
       <c r="C168" t="n">
         <v>117.3099975585938</v>
@@ -4813,11 +4825,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>105.6866073608398</v>
+        <v>105.6865997314453</v>
       </c>
       <c r="C169" t="n">
         <v>119.7600021362305</v>
@@ -4842,7 +4854,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4871,11 +4883,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>94.47123718261719</v>
+        <v>94.47122955322266</v>
       </c>
       <c r="C171" t="n">
         <v>106.5699996948242</v>
@@ -4900,11 +4912,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>76.28087615966797</v>
+        <v>76.28085327148438</v>
       </c>
       <c r="C172" t="n">
         <v>86.05000305175781</v>
@@ -4929,11 +4941,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>93.39786529541016</v>
+        <v>93.39785766601562</v>
       </c>
       <c r="C173" t="n">
         <v>104.75</v>
@@ -4958,11 +4970,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>116.2234954833984</v>
+        <v>116.2235107421875</v>
       </c>
       <c r="C174" t="n">
         <v>130.3500061035156</v>
@@ -4987,11 +4999,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>120.4765548706055</v>
+        <v>120.4765243530273</v>
       </c>
       <c r="C175" t="n">
         <v>135.1199951171875</v>
@@ -5016,11 +5028,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>133.2807312011719</v>
+        <v>133.28076171875</v>
       </c>
       <c r="C176" t="n">
         <v>148.9100036621094</v>
@@ -5045,11 +5057,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>147.4045867919922</v>
+        <v>147.4045562744141</v>
       </c>
       <c r="C177" t="n">
         <v>164.6900024414062</v>
@@ -5074,11 +5086,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>148.4517822265625</v>
+        <v>148.4517517089844</v>
       </c>
       <c r="C178" t="n">
         <v>165.8600006103516</v>
@@ -5103,11 +5115,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>141.9927062988281</v>
+        <v>141.99267578125</v>
       </c>
       <c r="C179" t="n">
         <v>158.1000061035156</v>
@@ -5132,11 +5144,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>139.9449615478516</v>
+        <v>139.9449920654297</v>
       </c>
       <c r="C180" t="n">
         <v>155.8200073242188</v>
@@ -5161,7 +5173,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5190,7 +5202,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5219,11 +5231,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>143.9788055419922</v>
+        <v>143.9788208007812</v>
       </c>
       <c r="C183" t="n">
         <v>159.75</v>
@@ -5248,11 +5260,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>171.4046020507812</v>
+        <v>171.4045715332031</v>
       </c>
       <c r="C184" t="n">
         <v>190.1799926757812</v>
@@ -5277,11 +5289,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>177.3970642089844</v>
+        <v>177.3970489501953</v>
       </c>
       <c r="C185" t="n">
         <v>196.25</v>
@@ -5306,11 +5318,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>176.1134643554688</v>
+        <v>176.1134948730469</v>
       </c>
       <c r="C186" t="n">
         <v>194.8300018310547</v>
@@ -5335,11 +5347,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>175.3360595703125</v>
+        <v>175.3360748291016</v>
       </c>
       <c r="C187" t="n">
         <v>193.9700012207031</v>
@@ -5364,11 +5376,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>174.9044189453125</v>
+        <v>174.9044036865234</v>
       </c>
       <c r="C188" t="n">
         <v>192.6900024414062</v>
@@ -5393,11 +5405,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>185.0706787109375</v>
+        <v>185.0706634521484</v>
       </c>
       <c r="C189" t="n">
         <v>203.8899993896484</v>
@@ -5422,11 +5434,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>184.1357269287109</v>
+        <v>184.1356811523438</v>
       </c>
       <c r="C190" t="n">
         <v>202.8600006103516</v>
@@ -5451,11 +5463,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>213.0065765380859</v>
+        <v>213.0065460205078</v>
       </c>
       <c r="C191" t="n">
         <v>233.8200073242188</v>
@@ -5480,7 +5492,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5509,11 +5521,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>235.4714813232422</v>
+        <v>235.4714660644531</v>
       </c>
       <c r="C193" t="n">
         <v>258.4800109863281</v>
@@ -5538,11 +5550,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>216.9353485107422</v>
+        <v>216.9353637695312</v>
       </c>
       <c r="C194" t="n">
         <v>237.3500061035156</v>
@@ -5567,7 +5579,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5596,11 +5608,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>184.7994842529297</v>
+        <v>184.7994995117188</v>
       </c>
       <c r="C196" t="n">
         <v>202.1900024414062</v>
@@ -5625,11 +5637,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>181.4543151855469</v>
+        <v>181.454345703125</v>
       </c>
       <c r="C197" t="n">
         <v>197.7299957275391</v>
@@ -5654,11 +5666,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>179.2243804931641</v>
+        <v>179.2243499755859</v>
       </c>
       <c r="C198" t="n">
         <v>195.3000030517578</v>
@@ -5683,11 +5695,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>160.2924499511719</v>
+        <v>160.2924346923828</v>
       </c>
       <c r="C199" t="n">
         <v>174.6699981689453</v>
@@ -5712,11 +5724,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>176.763671875</v>
+        <v>176.7636413574219</v>
       </c>
       <c r="C200" t="n">
         <v>191.5299987792969</v>
@@ -5741,11 +5753,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>179.1724090576172</v>
+        <v>179.1724548339844</v>
       </c>
       <c r="C201" t="n">
         <v>194.1399993896484</v>
@@ -5770,11 +5782,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>173.3304443359375</v>
+        <v>173.3304290771484</v>
       </c>
       <c r="C202" t="n">
         <v>187.8099975585938</v>
@@ -5799,7 +5811,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5828,11 +5840,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>197.2300415039062</v>
+        <v>197.2300872802734</v>
       </c>
       <c r="C204" t="n">
         <v>212.5500030517578</v>
@@ -5857,11 +5869,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>184.8794250488281</v>
+        <v>184.8793792724609</v>
       </c>
       <c r="C205" t="n">
         <v>199.2400054931641</v>
@@ -5886,11 +5898,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>194.2342987060547</v>
+        <v>194.2342834472656</v>
       </c>
       <c r="C206" t="n">
         <v>208.25</v>
@@ -5915,7 +5927,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5944,11 +5956,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>186.5115661621094</v>
+        <v>186.5115814208984</v>
       </c>
       <c r="C208" t="n">
         <v>199.9700012207031</v>
@@ -5973,11 +5985,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>194.8118286132812</v>
+        <v>194.8118591308594</v>
       </c>
       <c r="C209" t="n">
         <v>207.8300018310547</v>
@@ -6002,11 +6014,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>188.5315093994141</v>
+        <v>188.5315399169922</v>
       </c>
       <c r="C210" t="n">
         <v>201.1300048828125</v>
@@ -6031,11 +6043,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>211.5624542236328</v>
+        <v>211.5625</v>
       </c>
       <c r="C211" t="n">
         <v>225.6999969482422</v>
@@ -6060,11 +6072,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>220.6328735351562</v>
+        <v>220.6328277587891</v>
       </c>
       <c r="C212" t="n">
         <v>234.2700042724609</v>
@@ -6089,11 +6101,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>217.0634460449219</v>
+        <v>217.0634613037109</v>
       </c>
       <c r="C213" t="n">
         <v>230.4799957275391</v>
@@ -6118,11 +6130,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>195.7413635253906</v>
+        <v>195.7413482666016</v>
       </c>
       <c r="C214" t="n">
         <v>207.8399963378906</v>
@@ -6147,7 +6159,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6176,11 +6188,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>188.355712890625</v>
+        <v>188.3557281494141</v>
       </c>
       <c r="C216" t="n">
         <v>198.8300018310547</v>
@@ -6205,11 +6217,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>210.8261413574219</v>
+        <v>210.8261260986328</v>
       </c>
       <c r="C217" t="n">
         <v>222.5500030517578</v>
@@ -6234,11 +6246,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>202.6415100097656</v>
+        <v>202.6415252685547</v>
       </c>
       <c r="C218" t="n">
         <v>212.8399963378906</v>
@@ -6263,7 +6275,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6292,11 +6304,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>242.5243072509766</v>
+        <v>242.5242919921875</v>
       </c>
       <c r="C220" t="n">
         <v>254.7299957275391</v>
@@ -6321,7 +6333,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6350,11 +6362,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>211.6936645507812</v>
+        <v>211.6936798095703</v>
       </c>
       <c r="C222" t="n">
         <v>221.2899932861328</v>
@@ -6379,11 +6391,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>210.8997192382812</v>
+        <v>210.8996887207031</v>
       </c>
       <c r="C223" t="n">
         <v>220.4600067138672</v>
@@ -6408,7 +6420,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6437,7 +6449,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6466,7 +6478,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6495,7 +6507,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6524,11 +6536,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>262.99072265625</v>
+        <v>262.9906921386719</v>
       </c>
       <c r="C228" t="n">
         <v>272.4299926757812</v>
@@ -6553,11 +6565,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>238.248779296875</v>
+        <v>238.2487945556641</v>
       </c>
       <c r="C229" t="n">
         <v>246.8000030517578</v>
@@ -6582,7 +6594,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6611,7 +6623,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6640,11 +6652,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>226.1327056884766</v>
+        <v>226.1327209472656</v>
       </c>
       <c r="C232" t="n">
         <v>233.2299957275391</v>
@@ -6669,11 +6681,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>217.9008483886719</v>
+        <v>217.9008331298828</v>
       </c>
       <c r="C233" t="n">
         <v>223.5599975585938</v>
@@ -6698,11 +6710,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>220.0158996582031</v>
+        <v>220.0158843994141</v>
       </c>
       <c r="C234" t="n">
         <v>225.7299957275391</v>
@@ -6727,11 +6739,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>216.2536010742188</v>
+        <v>216.2536163330078</v>
       </c>
       <c r="C235" t="n">
         <v>221.8699951171875</v>
@@ -6756,7 +6768,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6785,7 +6797,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6814,7 +6826,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6872,7 +6884,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6901,7 +6913,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6930,7 +6942,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6959,7 +6971,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6988,7 +7000,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7017,7 +7029,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7046,7 +7058,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7075,7 +7087,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7104,7 +7116,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7133,7 +7145,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7162,32 +7174,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>191.3600006103516</v>
+        <v>188.4900054931641</v>
       </c>
       <c r="C250" t="n">
-        <v>191.3600006103516</v>
+        <v>188.4900054931641</v>
       </c>
       <c r="D250" t="n">
-        <v>50812300</v>
+        <v>54553900</v>
       </c>
       <c r="E250" t="n">
         <v>11.83</v>
       </c>
       <c r="F250" t="n">
-        <v>16.17582422741772</v>
+        <v>15.93322108987017</v>
       </c>
       <c r="G250" t="n">
         <v>561054019</v>
       </c>
       <c r="H250" t="n">
-        <v>107363297418.2802</v>
+        <v>105753075123.2718</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09056578917403674</v>
+        <v>0.09723466574080454</v>
       </c>
     </row>
   </sheetData>
@@ -7219,75 +7231,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39571</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39661</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7323,13 +7335,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39662</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39752</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7365,13 +7377,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39844</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39934</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40331</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7407,13 +7419,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39935</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7449,13 +7461,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7491,13 +7503,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40208</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40331</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7533,13 +7545,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7575,13 +7587,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7617,13 +7629,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40481</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40571</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40631</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7650,7 +7662,7 @@
       <c r="I10" t="n">
         <v>1.42</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40631</v>
       </c>
       <c r="K10" t="n">
@@ -7663,13 +7675,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40572</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7696,7 +7708,7 @@
       <c r="I11" t="n">
         <v>1.42</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="K11" t="n">
@@ -7709,13 +7721,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40785</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7742,7 +7754,7 @@
       <c r="I12" t="n">
         <v>1.48</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40785</v>
       </c>
       <c r="K12" t="n">
@@ -7755,13 +7767,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40754</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7788,7 +7800,7 @@
       <c r="I13" t="n">
         <v>1.37</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="K13" t="n">
@@ -7801,13 +7813,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40845</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40942</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41001</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7834,7 +7846,7 @@
       <c r="I14" t="n">
         <v>1.43</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41001</v>
       </c>
       <c r="K14" t="n">
@@ -7847,13 +7859,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40943</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41033</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41066</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7880,7 +7892,7 @@
       <c r="I15" t="n">
         <v>1.52</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41066</v>
       </c>
       <c r="K15" t="n">
@@ -7893,13 +7905,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41034</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41124</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41156</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7926,7 +7938,7 @@
       <c r="I16" t="n">
         <v>1.52</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41156</v>
       </c>
       <c r="K16" t="n">
@@ -7939,13 +7951,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41125</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41215</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41247</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7972,7 +7984,7 @@
       <c r="I17" t="n">
         <v>1.69</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41247</v>
       </c>
       <c r="K17" t="n">
@@ -7985,13 +7997,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41216</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41366</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8018,7 +8030,7 @@
       <c r="I18" t="n">
         <v>1.69</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41366</v>
       </c>
       <c r="K18" t="n">
@@ -8031,13 +8043,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41307</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41397</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41429</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8064,7 +8076,7 @@
       <c r="I19" t="n">
         <v>1.75</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41429</v>
       </c>
       <c r="K19" t="n">
@@ -8077,13 +8089,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41398</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41488</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41520</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8110,7 +8122,7 @@
       <c r="I20" t="n">
         <v>1.99</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41520</v>
       </c>
       <c r="K20" t="n">
@@ -8123,13 +8135,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41489</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41611</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8156,7 +8168,7 @@
       <c r="I21" t="n">
         <v>2.11</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41611</v>
       </c>
       <c r="K21" t="n">
@@ -8169,13 +8181,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41580</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8202,7 +8214,7 @@
       <c r="I22" t="n">
         <v>2.14</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="K22" t="n">
@@ -8215,13 +8227,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41761</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41793</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8248,7 +8260,7 @@
       <c r="I23" t="n">
         <v>2.26</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41793</v>
       </c>
       <c r="K23" t="n">
@@ -8261,13 +8273,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41762</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41884</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8294,7 +8306,7 @@
       <c r="I24" t="n">
         <v>2.42</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41884</v>
       </c>
       <c r="K24" t="n">
@@ -8307,13 +8319,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41853</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41975</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8340,7 +8352,7 @@
       <c r="I25" t="n">
         <v>2.54</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41975</v>
       </c>
       <c r="K25" t="n">
@@ -8353,13 +8365,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42034</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8386,7 +8398,7 @@
       <c r="I26" t="n">
         <v>2.71</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="K26" t="n">
@@ -8399,13 +8411,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42157</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8432,7 +8444,7 @@
       <c r="I27" t="n">
         <v>2.8</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42157</v>
       </c>
       <c r="K27" t="n">
@@ -8445,13 +8457,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42126</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8478,7 +8490,7 @@
       <c r="I28" t="n">
         <v>2.96</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="K28" t="n">
@@ -8491,13 +8503,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42340</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8524,7 +8536,7 @@
       <c r="I29" t="n">
         <v>3.17</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42340</v>
       </c>
       <c r="K29" t="n">
@@ -8537,13 +8549,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42458</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8570,7 +8582,7 @@
       <c r="I30" t="n">
         <v>2.73</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42458</v>
       </c>
       <c r="K30" t="n">
@@ -8583,13 +8595,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42399</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8616,7 +8628,7 @@
       <c r="I31" t="n">
         <v>3.01</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="K31" t="n">
@@ -8629,13 +8641,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42615</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8662,7 +8674,7 @@
       <c r="I32" t="n">
         <v>3.12</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42615</v>
       </c>
       <c r="K32" t="n">
@@ -8675,13 +8687,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42581</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42671</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42703</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8708,7 +8720,7 @@
       <c r="I33" t="n">
         <v>2.75</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42703</v>
       </c>
       <c r="K33" t="n">
@@ -8721,13 +8733,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42672</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42769</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42829</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8754,7 +8766,7 @@
       <c r="I34" t="n">
         <v>3.47</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42829</v>
       </c>
       <c r="K34" t="n">
@@ -8767,13 +8779,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42770</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42860</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42892</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8800,7 +8812,7 @@
       <c r="I35" t="n">
         <v>3.19</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42892</v>
       </c>
       <c r="K35" t="n">
@@ -8813,13 +8825,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42861</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42951</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42983</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8846,7 +8858,7 @@
       <c r="I36" t="n">
         <v>3.56</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42983</v>
       </c>
       <c r="K36" t="n">
@@ -8859,13 +8871,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42952</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43042</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43074</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8892,7 +8904,7 @@
       <c r="I37" t="n">
         <v>4.18</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43074</v>
       </c>
       <c r="K37" t="n">
@@ -8905,13 +8917,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43043</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43133</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43192</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8938,7 +8950,7 @@
       <c r="I38" t="n">
         <v>4.09</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43192</v>
       </c>
       <c r="K38" t="n">
@@ -8951,13 +8963,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43134</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43224</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43256</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8984,7 +8996,7 @@
       <c r="I39" t="n">
         <v>4.58</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43256</v>
       </c>
       <c r="K39" t="n">
@@ -8997,13 +9009,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43225</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43315</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43347</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9030,7 +9042,7 @@
       <c r="I40" t="n">
         <v>4.760000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43347</v>
       </c>
       <c r="K40" t="n">
@@ -9043,13 +9055,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43316</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43406</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43440</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9076,7 +9088,7 @@
       <c r="I41" t="n">
         <v>4.49</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43440</v>
       </c>
       <c r="K41" t="n">
@@ -9089,13 +9101,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43407</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43557</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9122,7 +9134,7 @@
       <c r="I42" t="n">
         <v>2.84</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43557</v>
       </c>
       <c r="K42" t="n">
@@ -9135,13 +9147,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43498</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43588</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43619</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9168,7 +9180,7 @@
       <c r="I43" t="n">
         <v>2.96</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43619</v>
       </c>
       <c r="K43" t="n">
@@ -9181,13 +9193,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43589</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43679</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43711</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9214,7 +9226,7 @@
       <c r="I44" t="n">
         <v>3.24</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43711</v>
       </c>
       <c r="K44" t="n">
@@ -9227,13 +9239,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43680</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43803</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9260,7 +9272,7 @@
       <c r="I45" t="n">
         <v>3.819999999999999</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43803</v>
       </c>
       <c r="K45" t="n">
@@ -9273,13 +9285,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43771</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9306,7 +9318,7 @@
       <c r="I46" t="n">
         <v>5.489999999999999</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="K46" t="n">
@@ -9319,13 +9331,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43979</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9352,7 +9364,7 @@
       <c r="I47" t="n">
         <v>5.94</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43979</v>
       </c>
       <c r="K47" t="n">
@@ -9365,13 +9377,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43953</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44069</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9398,7 +9410,7 @@
       <c r="I48" t="n">
         <v>7.539999999999999</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44069</v>
       </c>
       <c r="K48" t="n">
@@ -9411,13 +9423,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44134</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9444,7 +9456,7 @@
       <c r="I49" t="n">
         <v>7.089999999999999</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="K49" t="n">
@@ -9457,13 +9469,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44277</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9490,7 +9502,7 @@
       <c r="I50" t="n">
         <v>7.75</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44277</v>
       </c>
       <c r="K50" t="n">
@@ -9503,13 +9515,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44226</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44343</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9536,7 +9548,7 @@
       <c r="I51" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44343</v>
       </c>
       <c r="K51" t="n">
@@ -9549,13 +9561,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44434</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9582,7 +9594,7 @@
       <c r="I52" t="n">
         <v>9.709999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44434</v>
       </c>
       <c r="K52" t="n">
@@ -9595,13 +9607,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9628,7 +9640,7 @@
       <c r="I53" t="n">
         <v>11.53</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="K53" t="n">
@@ -9641,13 +9653,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44499</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44589</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44641</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9674,7 +9686,7 @@
       <c r="I54" t="n">
         <v>12.04</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44641</v>
       </c>
       <c r="K54" t="n">
@@ -9687,13 +9699,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44590</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44707</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9720,7 +9732,7 @@
       <c r="I55" t="n">
         <v>12.34</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44707</v>
       </c>
       <c r="K55" t="n">
@@ -9733,13 +9745,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44798</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9766,7 +9778,7 @@
       <c r="I56" t="n">
         <v>12.76</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44798</v>
       </c>
       <c r="K56" t="n">
@@ -9779,13 +9791,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44772</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44888</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9812,7 +9824,7 @@
       <c r="I57" t="n">
         <v>10.28</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44888</v>
       </c>
       <c r="K57" t="n">
@@ -9825,13 +9837,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44863</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44960</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45012</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9858,7 +9870,7 @@
       <c r="I58" t="n">
         <v>10.17</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45012</v>
       </c>
       <c r="K58" t="n">
@@ -9871,13 +9883,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44961</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45051</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9904,7 +9916,7 @@
       <c r="I59" t="n">
         <v>10.43</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="K59" t="n">
@@ -9917,13 +9929,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45052</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45142</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45168</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9950,7 +9962,7 @@
       <c r="I60" t="n">
         <v>10.32</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45168</v>
       </c>
       <c r="K60" t="n">
@@ -9963,13 +9975,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45143</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45233</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45259</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9996,7 +10008,7 @@
       <c r="I61" t="n">
         <v>13.13</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45259</v>
       </c>
       <c r="K61" t="n">
@@ -10009,13 +10021,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45234</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45324</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10042,7 +10054,7 @@
       <c r="I62" t="n">
         <v>13.2</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="K62" t="n">
@@ -10055,13 +10067,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45325</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45415</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10088,7 +10100,7 @@
       <c r="I63" t="n">
         <v>12.49</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="K63" t="n">
@@ -10101,13 +10113,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45416</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45506</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10134,7 +10146,7 @@
       <c r="I64" t="n">
         <v>12.1</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="K64" t="n">
@@ -10147,13 +10159,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45507</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10180,7 +10192,7 @@
       <c r="I65" t="n">
         <v>12.03</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="K65" t="n">
@@ -10193,13 +10205,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45598</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10226,7 +10238,7 @@
       <c r="I66" t="n">
         <v>12.23</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="K66" t="n">
@@ -10239,13 +10251,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45689</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45779</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10272,7 +10284,7 @@
       <c r="I67" t="n">
         <v>12.09</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="K67" t="n">
@@ -10285,13 +10297,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45780</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10318,7 +10330,7 @@
       <c r="I68" t="n">
         <v>12.19</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="K68" t="n">
@@ -10331,13 +10343,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45871</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10364,7 +10376,7 @@
       <c r="I69" t="n">
         <v>12.08</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="K69" t="n">
@@ -10377,13 +10389,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46104</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10410,7 +10422,7 @@
       <c r="I70" t="n">
         <v>11.85</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46104</v>
       </c>
       <c r="K70" t="n">
@@ -10423,13 +10435,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10456,7 +10468,7 @@
       <c r="I71" t="n">
         <v>11.83</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="K71" t="n">
@@ -10469,13 +10481,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10502,7 +10514,7 @@
       <c r="I72" t="n">
         <v>11.83</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="K72" t="n">
@@ -10539,52 +10551,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40053</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="C2" t="n">
@@ -10613,10 +10625,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40144</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="C3" t="n">
@@ -10645,10 +10657,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40263</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40267</v>
       </c>
       <c r="C4" t="n">
@@ -10677,10 +10689,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40326</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40331</v>
       </c>
       <c r="C5" t="n">
@@ -10709,10 +10721,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40417</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="C6" t="n">
@@ -10741,10 +10753,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40508</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="C7" t="n">
@@ -10773,10 +10785,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40627</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40631</v>
       </c>
       <c r="C8" t="n">
@@ -10805,10 +10817,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40690</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="C9" t="n">
@@ -10837,10 +10849,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40781</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40785</v>
       </c>
       <c r="C10" t="n">
@@ -10869,10 +10881,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40872</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="C11" t="n">
@@ -10901,10 +10913,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40998</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41001</v>
       </c>
       <c r="C12" t="n">
@@ -10933,10 +10945,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41061</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41066</v>
       </c>
       <c r="C13" t="n">
@@ -10965,10 +10977,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41156</v>
       </c>
       <c r="C14" t="n">
@@ -10997,10 +11009,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41247</v>
       </c>
       <c r="C15" t="n">
@@ -11029,10 +11041,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41361</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41366</v>
       </c>
       <c r="C16" t="n">
@@ -11061,10 +11073,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41425</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41429</v>
       </c>
       <c r="C17" t="n">
@@ -11093,10 +11105,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41516</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41520</v>
       </c>
       <c r="C18" t="n">
@@ -11125,10 +11137,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41607</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41611</v>
       </c>
       <c r="C19" t="n">
@@ -11157,10 +11169,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41726</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="C20" t="n">
@@ -11189,10 +11201,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41789</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41793</v>
       </c>
       <c r="C21" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41880</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41884</v>
       </c>
       <c r="C22" t="n">
@@ -11253,10 +11265,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41971</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41975</v>
       </c>
       <c r="C23" t="n">
@@ -11285,10 +11297,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42090</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="C24" t="n">
@@ -11317,10 +11329,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42153</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42157</v>
       </c>
       <c r="C25" t="n">
@@ -11349,10 +11361,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42244</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="C26" t="n">
@@ -11381,10 +11393,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42335</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42340</v>
       </c>
       <c r="C27" t="n">
@@ -11413,10 +11425,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42453</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42458</v>
       </c>
       <c r="C28" t="n">
@@ -11445,10 +11457,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42517</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="C29" t="n">
@@ -11477,10 +11489,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42608</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42615</v>
       </c>
       <c r="C30" t="n">
@@ -11509,10 +11521,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42699</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42703</v>
       </c>
       <c r="C31" t="n">
@@ -11541,10 +11553,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42829</v>
       </c>
       <c r="C32" t="n">
@@ -11573,10 +11585,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42888</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42892</v>
       </c>
       <c r="C33" t="n">
@@ -11605,10 +11617,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42979</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42983</v>
       </c>
       <c r="C34" t="n">
@@ -11637,10 +11649,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43070</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43074</v>
       </c>
       <c r="C35" t="n">
@@ -11669,10 +11681,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43188</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43192</v>
       </c>
       <c r="C36" t="n">
@@ -11701,10 +11713,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43252</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43256</v>
       </c>
       <c r="C37" t="n">
@@ -11733,10 +11745,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43343</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43347</v>
       </c>
       <c r="C38" t="n">
@@ -11765,10 +11777,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43440</v>
       </c>
       <c r="C39" t="n">
@@ -11797,10 +11809,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43553</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43557</v>
       </c>
       <c r="C40" t="n">
@@ -11829,10 +11841,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43614</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43619</v>
       </c>
       <c r="C41" t="n">
@@ -11861,10 +11873,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43707</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43711</v>
       </c>
       <c r="C42" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43798</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43803</v>
       </c>
       <c r="C43" t="n">
@@ -11925,10 +11937,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43903</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="C44" t="n">
@@ -11957,10 +11969,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43977</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43979</v>
       </c>
       <c r="C45" t="n">
@@ -11989,10 +12001,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44067</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44069</v>
       </c>
       <c r="C46" t="n">
@@ -12021,10 +12033,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44158</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="C47" t="n">
@@ -12053,10 +12065,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44274</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44277</v>
       </c>
       <c r="C48" t="n">
@@ -12085,10 +12097,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44341</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44343</v>
       </c>
       <c r="C49" t="n">
@@ -12117,10 +12129,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44432</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44434</v>
       </c>
       <c r="C50" t="n">
@@ -12149,10 +12161,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44522</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="C51" t="n">
@@ -12181,10 +12193,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44637</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44641</v>
       </c>
       <c r="C52" t="n">
@@ -12213,10 +12225,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44705</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44707</v>
       </c>
       <c r="C53" t="n">
@@ -12245,10 +12257,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44796</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44798</v>
       </c>
       <c r="C54" t="n">
@@ -12277,10 +12289,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44886</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44888</v>
       </c>
       <c r="C55" t="n">
@@ -12309,10 +12321,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45008</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45012</v>
       </c>
       <c r="C56" t="n">
@@ -12341,10 +12353,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45076</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="C57" t="n">
@@ -12373,10 +12385,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45168</v>
       </c>
       <c r="C58" t="n">
@@ -12405,10 +12417,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45257</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45259</v>
       </c>
       <c r="C59" t="n">
@@ -12437,10 +12449,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45372</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="C60" t="n">
@@ -12469,10 +12481,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45440</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="C61" t="n">
@@ -12501,10 +12513,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45531</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="C62" t="n">
@@ -12533,10 +12545,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45621</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="C63" t="n">
@@ -12565,10 +12577,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45736</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="C64" t="n">
@@ -12597,10 +12609,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45804</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="C65" t="n">
@@ -12629,10 +12641,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45895</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="C66" t="n">
@@ -12661,10 +12673,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45985</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="C67" t="n">
@@ -12693,10 +12705,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46104</v>
       </c>
       <c r="C68" t="n">
@@ -12725,10 +12737,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46168</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="C69" t="n">
@@ -12757,10 +12769,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46259</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="C70" t="n">
@@ -12807,12 +12819,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/LOW.xlsx
+++ b/salidas/empresas/LOW.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>22.29584503173828</v>
+        <v>22.29584693908691</v>
       </c>
       <c r="C2" t="n">
         <v>31.77499961853027</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>23.92023277282715</v>
+        <v>23.92024040222168</v>
       </c>
       <c r="C3" t="n">
         <v>34.09000015258789</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>22.14113235473633</v>
+        <v>22.14114189147949</v>
       </c>
       <c r="C5" t="n">
         <v>31.52499961853027</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>21.30536651611328</v>
+        <v>21.30535316467285</v>
       </c>
       <c r="C7" t="n">
         <v>30.33499908447266</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>19.94714736938477</v>
+        <v>19.94713401794434</v>
       </c>
       <c r="C8" t="n">
         <v>28.35000038146973</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>19.03948211669922</v>
+        <v>19.03949165344238</v>
       </c>
       <c r="C9" t="n">
         <v>27.05999946594238</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>19.74309349060059</v>
+        <v>19.74308776855469</v>
       </c>
       <c r="C10" t="n">
         <v>28.05999946594238</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>21.25544929504395</v>
+        <v>21.25545120239258</v>
       </c>
       <c r="C12" t="n">
         <v>30.15999984741211</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>21.95315170288086</v>
+        <v>21.95315551757812</v>
       </c>
       <c r="C13" t="n">
         <v>31.14999961853027</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>23.79294967651367</v>
+        <v>23.79294776916504</v>
       </c>
       <c r="C14" t="n">
         <v>33.70999908447266</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>22.97421646118164</v>
+        <v>22.97420883178711</v>
       </c>
       <c r="C15" t="n">
         <v>32.54999923706055</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>21.60357093811035</v>
+        <v>21.60356330871582</v>
       </c>
       <c r="C17" t="n">
         <v>30.55999946594238</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>23.20120811462402</v>
+        <v>23.20120429992676</v>
       </c>
       <c r="C18" t="n">
         <v>32.81999969482422</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>21.69546127319336</v>
+        <v>21.69547271728516</v>
       </c>
       <c r="C19" t="n">
         <v>30.69000053405762</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>19.85410690307617</v>
+        <v>19.85409927368164</v>
       </c>
       <c r="C20" t="n">
         <v>28.01000022888184</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>22.01601219177246</v>
+        <v>22.01601409912109</v>
       </c>
       <c r="C21" t="n">
         <v>31.05999946594238</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>19.86118698120117</v>
+        <v>19.86118507385254</v>
       </c>
       <c r="C22" t="n">
         <v>28.02000045776367</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>18.8609733581543</v>
+        <v>18.86098480224609</v>
       </c>
       <c r="C26" t="n">
         <v>26.43000030517578</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>17.10547065734863</v>
+        <v>17.10546875</v>
       </c>
       <c r="C27" t="n">
         <v>23.96999931335449</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>16.37043571472168</v>
+        <v>16.37044906616211</v>
       </c>
       <c r="C28" t="n">
         <v>22.94000053405762</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>17.18369293212891</v>
+        <v>17.18368530273438</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>14.85672760009766</v>
+        <v>14.85672569274902</v>
       </c>
       <c r="C31" t="n">
         <v>20.75</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>14.61682415008545</v>
+        <v>14.61682033538818</v>
       </c>
       <c r="C32" t="n">
         <v>20.31999969482422</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>17.72433662414551</v>
+        <v>17.72433280944824</v>
       </c>
       <c r="C33" t="n">
         <v>24.63999938964844</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>17.04097366333008</v>
+        <v>17.04096984863281</v>
       </c>
       <c r="C34" t="n">
         <v>23.69000053405762</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>15.6790189743042</v>
+        <v>15.67902278900146</v>
       </c>
       <c r="C35" t="n">
         <v>21.70000076293945</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>14.92758464813232</v>
+        <v>14.92758655548096</v>
       </c>
       <c r="C36" t="n">
         <v>20.65999984741211</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>15.54896545410156</v>
+        <v>15.54895401000977</v>
       </c>
       <c r="C37" t="n">
         <v>21.52000045776367</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.25622844696045</v>
+        <v>13.25622749328613</v>
       </c>
       <c r="C38" t="n">
         <v>18.27000045776367</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>11.49308681488037</v>
+        <v>11.49308490753174</v>
       </c>
       <c r="C39" t="n">
         <v>15.84000015258789</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>13.24171829223633</v>
+        <v>13.24171352386475</v>
       </c>
       <c r="C40" t="n">
         <v>18.25</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>13.85252952575684</v>
+        <v>13.85253047943115</v>
       </c>
       <c r="C42" t="n">
         <v>19.01000022888184</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.14401531219482</v>
+        <v>14.14400672912598</v>
       </c>
       <c r="C43" t="n">
         <v>19.40999984741211</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>16.44215202331543</v>
+        <v>16.4421443939209</v>
       </c>
       <c r="C44" t="n">
         <v>22.45999908447266</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>15.73937511444092</v>
+        <v>15.73937320709229</v>
       </c>
       <c r="C45" t="n">
         <v>21.5</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>15.32941246032715</v>
+        <v>15.32941341400146</v>
       </c>
       <c r="C46" t="n">
         <v>20.94000053405762</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>14.38685131072998</v>
+        <v>14.38685417175293</v>
       </c>
       <c r="C47" t="n">
         <v>19.56999969482422</v>
@@ -1409,7 +1409,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>17.19511985778809</v>
+        <v>17.19511795043945</v>
       </c>
       <c r="C49" t="n">
         <v>23.38999938964844</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>15.97796440124512</v>
+        <v>15.97797107696533</v>
       </c>
       <c r="C50" t="n">
         <v>21.64999961853027</v>
@@ -1484,7 +1484,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>17.8894214630127</v>
+        <v>17.88942527770996</v>
       </c>
       <c r="C52" t="n">
         <v>24.23999977111816</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>18.32855415344238</v>
+        <v>18.32855033874512</v>
       </c>
       <c r="C54" t="n">
         <v>24.75</v>
@@ -1559,7 +1559,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>15.12197780609131</v>
+        <v>15.12198257446289</v>
       </c>
       <c r="C55" t="n">
         <v>20.42000007629395</v>
@@ -1584,7 +1584,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>15.44372367858887</v>
+        <v>15.44372844696045</v>
       </c>
       <c r="C56" t="n">
         <v>20.73999977111816</v>
@@ -1609,7 +1609,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>15.10120010375977</v>
+        <v>15.10118961334229</v>
       </c>
       <c r="C57" t="n">
         <v>20.28000068664551</v>
@@ -1634,7 +1634,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>16.5979118347168</v>
+        <v>16.59790992736816</v>
       </c>
       <c r="C58" t="n">
         <v>22.29000091552734</v>
@@ -1659,7 +1659,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>15.97199821472168</v>
+        <v>15.97199630737305</v>
       </c>
       <c r="C59" t="n">
         <v>21.34000015258789</v>
@@ -1684,7 +1684,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>16.98989868164062</v>
+        <v>16.98989486694336</v>
       </c>
       <c r="C60" t="n">
         <v>22.70000076293945</v>
@@ -1709,7 +1709,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>18.77121925354004</v>
+        <v>18.77121734619141</v>
       </c>
       <c r="C61" t="n">
         <v>25.07999992370605</v>
@@ -1734,7 +1734,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>18.64518737792969</v>
+        <v>18.64518356323242</v>
       </c>
       <c r="C62" t="n">
         <v>24.79999923706055</v>
@@ -1759,7 +1759,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>19.67519187927246</v>
+        <v>19.67518424987793</v>
       </c>
       <c r="C63" t="n">
         <v>26.17000007629395</v>
@@ -1784,7 +1784,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>19.87066078186035</v>
+        <v>19.87065696716309</v>
       </c>
       <c r="C64" t="n">
         <v>26.43000030517578</v>
@@ -1842,7 +1842,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>18.22309112548828</v>
+        <v>18.22310256958008</v>
       </c>
       <c r="C66" t="n">
         <v>24.13999938964844</v>
@@ -1871,7 +1871,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>17.59653091430664</v>
+        <v>17.59652900695801</v>
       </c>
       <c r="C67" t="n">
         <v>23.30999946594238</v>
@@ -1900,7 +1900,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>16.39094543457031</v>
+        <v>16.39095878601074</v>
       </c>
       <c r="C68" t="n">
         <v>21.57999992370605</v>
@@ -1929,7 +1929,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>15.13770484924316</v>
+        <v>15.13770294189453</v>
       </c>
       <c r="C69" t="n">
         <v>19.93000030517578</v>
@@ -1958,7 +1958,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>14.68957710266113</v>
+        <v>14.68957614898682</v>
       </c>
       <c r="C70" t="n">
         <v>19.34000015258789</v>
@@ -1987,7 +1987,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>16.07311630249023</v>
+        <v>16.07312202453613</v>
       </c>
       <c r="C71" t="n">
         <v>21.02000045776367</v>
@@ -2016,7 +2016,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>18.35944557189941</v>
+        <v>18.35944366455078</v>
       </c>
       <c r="C72" t="n">
         <v>24.01000022888184</v>
@@ -2045,7 +2045,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>19.40702247619629</v>
+        <v>19.40702819824219</v>
       </c>
       <c r="C73" t="n">
         <v>25.3799991607666</v>
@@ -2074,7 +2074,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>20.62462425231934</v>
+        <v>20.62461471557617</v>
       </c>
       <c r="C74" t="n">
         <v>26.82999992370605</v>
@@ -2103,7 +2103,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>21.81612777709961</v>
+        <v>21.81613159179688</v>
       </c>
       <c r="C75" t="n">
         <v>28.3799991607666</v>
@@ -2190,7 +2190,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>20.63132667541504</v>
+        <v>20.63132476806641</v>
       </c>
       <c r="C78" t="n">
         <v>26.71999931335449</v>
@@ -2219,7 +2219,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>21.95938873291016</v>
+        <v>21.95939064025879</v>
       </c>
       <c r="C79" t="n">
         <v>28.44000053405762</v>
@@ -2248,7 +2248,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>19.71124267578125</v>
+        <v>19.71123504638672</v>
       </c>
       <c r="C80" t="n">
         <v>25.3700008392334</v>
@@ -2277,7 +2277,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>22.1275463104248</v>
+        <v>22.12755012512207</v>
       </c>
       <c r="C81" t="n">
         <v>28.47999954223633</v>
@@ -2306,7 +2306,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>23.4949836730957</v>
+        <v>23.49497604370117</v>
       </c>
       <c r="C82" t="n">
         <v>30.23999977111816</v>
@@ -2364,7 +2364,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>28.17827224731445</v>
+        <v>28.17827606201172</v>
       </c>
       <c r="C84" t="n">
         <v>36.09000015258789</v>
@@ -2393,7 +2393,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>27.73323440551758</v>
+        <v>27.73323249816895</v>
       </c>
       <c r="C85" t="n">
         <v>35.52000045776367</v>
@@ -2422,7 +2422,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>29.94740867614746</v>
+        <v>29.9474048614502</v>
       </c>
       <c r="C86" t="n">
         <v>38.18999862670898</v>
@@ -2451,7 +2451,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>29.91604232788086</v>
+        <v>29.91604423522949</v>
       </c>
       <c r="C87" t="n">
         <v>38.15000152587891</v>
@@ -2480,7 +2480,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>29.73567962646484</v>
+        <v>29.73568344116211</v>
       </c>
       <c r="C88" t="n">
         <v>37.91999816894531</v>
@@ -2509,7 +2509,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>30.2547435760498</v>
+        <v>30.25475311279297</v>
       </c>
       <c r="C89" t="n">
         <v>38.41999816894531</v>
@@ -2538,7 +2538,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>33.16053771972656</v>
+        <v>33.1605339050293</v>
       </c>
       <c r="C90" t="n">
         <v>42.11000061035156</v>
@@ -2567,7 +2567,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>32.20770645141602</v>
+        <v>32.20769119262695</v>
       </c>
       <c r="C91" t="n">
         <v>40.90000152587891</v>
@@ -2596,7 +2596,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>35.24890899658203</v>
+        <v>35.24891662597656</v>
       </c>
       <c r="C92" t="n">
         <v>44.58000183105469</v>
@@ -2625,7 +2625,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>36.2293701171875</v>
+        <v>36.2293586730957</v>
       </c>
       <c r="C93" t="n">
         <v>45.81999969482422</v>
@@ -2654,7 +2654,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>37.64470672607422</v>
+        <v>37.64471054077148</v>
       </c>
       <c r="C94" t="n">
         <v>47.61000061035156</v>
@@ -2683,7 +2683,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>39.50970840454102</v>
+        <v>39.50971221923828</v>
       </c>
       <c r="C95" t="n">
         <v>49.77999877929688</v>
@@ -2712,7 +2712,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>37.68421936035156</v>
+        <v>37.68424224853516</v>
       </c>
       <c r="C96" t="n">
         <v>47.47999954223633</v>
@@ -2741,7 +2741,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>39.32717132568359</v>
+        <v>39.32716369628906</v>
       </c>
       <c r="C97" t="n">
         <v>49.54999923706055</v>
@@ -2770,7 +2770,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>36.87752151489258</v>
+        <v>36.87751388549805</v>
       </c>
       <c r="C98" t="n">
         <v>46.29000091552734</v>
@@ -2799,7 +2799,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>39.85703277587891</v>
+        <v>39.85704040527344</v>
       </c>
       <c r="C99" t="n">
         <v>50.02999877929688</v>
@@ -2828,7 +2828,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>38.95681762695312</v>
+        <v>38.95680999755859</v>
       </c>
       <c r="C100" t="n">
         <v>48.90000152587891</v>
@@ -2857,7 +2857,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>36.71600723266602</v>
+        <v>36.71600341796875</v>
       </c>
       <c r="C101" t="n">
         <v>45.90999984741211</v>
@@ -2886,7 +2886,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>37.65171051025391</v>
+        <v>37.65169906616211</v>
       </c>
       <c r="C102" t="n">
         <v>47.08000183105469</v>
@@ -2915,7 +2915,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>38.37946701049805</v>
+        <v>38.37947082519531</v>
       </c>
       <c r="C103" t="n">
         <v>47.9900016784668</v>
@@ -2944,7 +2944,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>38.45248031616211</v>
+        <v>38.45248794555664</v>
       </c>
       <c r="C104" t="n">
         <v>47.84999847412109</v>
@@ -2973,7 +2973,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>42.19729232788086</v>
+        <v>42.1972770690918</v>
       </c>
       <c r="C105" t="n">
         <v>52.5099983215332</v>
@@ -3002,7 +3002,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>42.52675628662109</v>
+        <v>42.52676010131836</v>
       </c>
       <c r="C106" t="n">
         <v>52.91999816894531</v>
@@ -3031,7 +3031,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>46.16841506958008</v>
+        <v>46.16840362548828</v>
       </c>
       <c r="C107" t="n">
         <v>57.20000076293945</v>
@@ -3089,7 +3089,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>55.5312385559082</v>
+        <v>55.53125762939453</v>
       </c>
       <c r="C109" t="n">
         <v>68.80000305175781</v>
@@ -3118,7 +3118,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>54.88206100463867</v>
+        <v>54.88205718994141</v>
       </c>
       <c r="C110" t="n">
         <v>67.76000213623047</v>
@@ -3147,7 +3147,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>60.00902938842773</v>
+        <v>60.009033203125</v>
       </c>
       <c r="C111" t="n">
         <v>74.08999633789062</v>
@@ -3176,7 +3176,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>60.25200653076172</v>
+        <v>60.25203323364258</v>
       </c>
       <c r="C112" t="n">
         <v>74.38999938964844</v>
@@ -3205,7 +3205,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>55.95038986206055</v>
+        <v>55.95037460327148</v>
       </c>
       <c r="C113" t="n">
         <v>68.86000061035156</v>
@@ -3234,7 +3234,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>56.86040115356445</v>
+        <v>56.86040878295898</v>
       </c>
       <c r="C114" t="n">
         <v>69.98000335693359</v>
@@ -3263,7 +3263,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>54.41471099853516</v>
+        <v>54.41470718383789</v>
       </c>
       <c r="C115" t="n">
         <v>66.97000122070312</v>
@@ -3292,7 +3292,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>56.59126663208008</v>
+        <v>56.59128570556641</v>
       </c>
       <c r="C116" t="n">
         <v>69.36000061035156</v>
@@ -3321,7 +3321,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>56.43625640869141</v>
+        <v>56.43624496459961</v>
       </c>
       <c r="C117" t="n">
         <v>69.16999816894531</v>
@@ -3350,7 +3350,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>56.23228073120117</v>
+        <v>56.23226165771484</v>
       </c>
       <c r="C118" t="n">
         <v>68.91999816894531</v>
@@ -3379,7 +3379,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>60.47101974487305</v>
+        <v>60.47103500366211</v>
       </c>
       <c r="C119" t="n">
         <v>73.83000183105469</v>
@@ -3408,7 +3408,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>62.73983001708984</v>
+        <v>62.73981857299805</v>
       </c>
       <c r="C120" t="n">
         <v>76.59999847412109</v>
@@ -3437,7 +3437,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>62.28113555908203</v>
+        <v>62.2811393737793</v>
       </c>
       <c r="C121" t="n">
         <v>76.04000091552734</v>
@@ -3466,7 +3466,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>58.92971038818359</v>
+        <v>58.92967224121094</v>
       </c>
       <c r="C122" t="n">
         <v>71.66000366210938</v>
@@ -3495,7 +3495,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>55.53337860107422</v>
+        <v>55.53339385986328</v>
       </c>
       <c r="C123" t="n">
         <v>67.52999877929688</v>
@@ -3524,7 +3524,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>62.2931022644043</v>
+        <v>62.29310989379883</v>
       </c>
       <c r="C124" t="n">
         <v>75.75</v>
@@ -3553,7 +3553,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>62.74238586425781</v>
+        <v>62.74236297607422</v>
       </c>
       <c r="C125" t="n">
         <v>76.01999664306641</v>
@@ -3582,7 +3582,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>66.13451385498047</v>
+        <v>66.13453674316406</v>
       </c>
       <c r="C126" t="n">
         <v>80.12999725341797</v>
@@ -3611,7 +3611,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>65.34220123291016</v>
+        <v>65.34220886230469</v>
       </c>
       <c r="C127" t="n">
         <v>79.16999816894531</v>
@@ -3640,7 +3640,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>68.20127105712891</v>
+        <v>68.20128631591797</v>
       </c>
       <c r="C128" t="n">
         <v>82.27999877929688</v>
@@ -3669,7 +3669,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>63.46001434326172</v>
+        <v>63.46001815795898</v>
       </c>
       <c r="C129" t="n">
         <v>76.55999755859375</v>
@@ -3698,7 +3698,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>59.85433197021484</v>
+        <v>59.85435104370117</v>
       </c>
       <c r="C130" t="n">
         <v>72.20999908447266</v>
@@ -3727,7 +3727,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>55.51803588867188</v>
+        <v>55.51804351806641</v>
       </c>
       <c r="C131" t="n">
         <v>66.65000152587891</v>
@@ -3756,7 +3756,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>58.76666641235352</v>
+        <v>58.76665115356445</v>
       </c>
       <c r="C132" t="n">
         <v>70.55000305175781</v>
@@ -3785,7 +3785,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>59.24143981933594</v>
+        <v>59.24144744873047</v>
       </c>
       <c r="C133" t="n">
         <v>71.12000274658203</v>
@@ -3814,7 +3814,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>61.17245864868164</v>
+        <v>61.17246627807617</v>
       </c>
       <c r="C134" t="n">
         <v>73.08000183105469</v>
@@ -3843,7 +3843,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>62.25225830078125</v>
+        <v>62.25224685668945</v>
       </c>
       <c r="C135" t="n">
         <v>74.37000274658203</v>
@@ -3901,7 +3901,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>71.34894561767578</v>
+        <v>71.34896087646484</v>
       </c>
       <c r="C137" t="n">
         <v>84.87999725341797</v>
@@ -3959,7 +3959,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>65.17061614990234</v>
+        <v>65.170654296875</v>
       </c>
       <c r="C139" t="n">
         <v>77.52999877929688</v>
@@ -3988,7 +3988,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>65.42465209960938</v>
+        <v>65.42463684082031</v>
       </c>
       <c r="C140" t="n">
         <v>77.40000152587891</v>
@@ -4017,7 +4017,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>62.45769882202148</v>
+        <v>62.45771789550781</v>
       </c>
       <c r="C141" t="n">
         <v>73.88999938964844</v>
@@ -4075,7 +4075,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>67.92645263671875</v>
+        <v>67.92646026611328</v>
       </c>
       <c r="C143" t="n">
         <v>79.94999694824219</v>
@@ -4104,7 +4104,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>70.83212280273438</v>
+        <v>70.83213043212891</v>
       </c>
       <c r="C144" t="n">
         <v>83.37000274658203</v>
@@ -4162,7 +4162,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>89.32175445556641</v>
+        <v>89.32174682617188</v>
       </c>
       <c r="C146" t="n">
         <v>104.7300033569336</v>
@@ -4191,7 +4191,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>76.40918731689453</v>
+        <v>76.40920257568359</v>
       </c>
       <c r="C147" t="n">
         <v>89.58999633789062</v>
@@ -4220,7 +4220,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>74.83988952636719</v>
+        <v>74.83990478515625</v>
       </c>
       <c r="C148" t="n">
         <v>87.75</v>
@@ -4249,7 +4249,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>70.64600372314453</v>
+        <v>70.64595794677734</v>
       </c>
       <c r="C149" t="n">
         <v>82.43000030517578</v>
@@ -4278,7 +4278,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>81.42758178710938</v>
+        <v>81.42758941650391</v>
       </c>
       <c r="C150" t="n">
         <v>95.01000213623047</v>
@@ -4307,7 +4307,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>81.90752410888672</v>
+        <v>81.90753173828125</v>
       </c>
       <c r="C151" t="n">
         <v>95.56999969482422</v>
@@ -4336,7 +4336,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>85.54447174072266</v>
+        <v>85.54447937011719</v>
       </c>
       <c r="C152" t="n">
         <v>99.33999633789062</v>
@@ -4365,7 +4365,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>93.64768218994141</v>
+        <v>93.64769744873047</v>
       </c>
       <c r="C153" t="n">
         <v>108.75</v>
@@ -4394,7 +4394,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>98.87473297119141</v>
+        <v>98.87474822998047</v>
       </c>
       <c r="C154" t="n">
         <v>114.8199996948242</v>
@@ -4423,7 +4423,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>82.39861297607422</v>
+        <v>82.39859771728516</v>
       </c>
       <c r="C155" t="n">
         <v>95.22000122070312</v>
@@ -4481,7 +4481,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>79.9237060546875</v>
+        <v>79.92371368408203</v>
       </c>
       <c r="C157" t="n">
         <v>92.36000061035156</v>
@@ -4539,7 +4539,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>91.40150451660156</v>
+        <v>91.40151977539062</v>
       </c>
       <c r="C159" t="n">
         <v>105.0899963378906</v>
@@ -4568,7 +4568,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>95.21102905273438</v>
+        <v>95.21101379394531</v>
       </c>
       <c r="C160" t="n">
         <v>109.4700012207031</v>
@@ -4597,7 +4597,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>98.82115173339844</v>
+        <v>98.82117462158203</v>
       </c>
       <c r="C161" t="n">
         <v>113.1399993896484</v>
@@ -4626,7 +4626,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>81.47461700439453</v>
+        <v>81.47459411621094</v>
       </c>
       <c r="C162" t="n">
         <v>93.27999877929688</v>
@@ -4655,7 +4655,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>88.13895416259766</v>
+        <v>88.13896942138672</v>
       </c>
       <c r="C163" t="n">
         <v>100.9100036621094</v>
@@ -4713,7 +4713,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>98.52857208251953</v>
+        <v>98.52855682373047</v>
       </c>
       <c r="C165" t="n">
         <v>112.1999969482422</v>
@@ -4742,7 +4742,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>96.56150054931641</v>
+        <v>96.56148529052734</v>
       </c>
       <c r="C166" t="n">
         <v>109.9599990844727</v>
@@ -4771,7 +4771,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>98.49434661865234</v>
+        <v>98.49433898925781</v>
       </c>
       <c r="C167" t="n">
         <v>111.6100006103516</v>
@@ -4829,7 +4829,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>105.6865997314453</v>
+        <v>105.6866073608398</v>
       </c>
       <c r="C169" t="n">
         <v>119.7600021362305</v>
@@ -4858,7 +4858,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>103.0434265136719</v>
+        <v>103.0434341430664</v>
       </c>
       <c r="C170" t="n">
         <v>116.2399978637695</v>
@@ -4887,7 +4887,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>94.47122955322266</v>
+        <v>94.47124481201172</v>
       </c>
       <c r="C171" t="n">
         <v>106.5699996948242</v>
@@ -4916,7 +4916,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>76.28085327148438</v>
+        <v>76.28084564208984</v>
       </c>
       <c r="C172" t="n">
         <v>86.05000305175781</v>
@@ -4945,7 +4945,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>93.39785766601562</v>
+        <v>93.39784240722656</v>
       </c>
       <c r="C173" t="n">
         <v>104.75</v>
@@ -4974,7 +4974,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>116.2235107421875</v>
+        <v>116.223518371582</v>
       </c>
       <c r="C174" t="n">
         <v>130.3500061035156</v>
@@ -5003,7 +5003,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>120.4765243530273</v>
+        <v>120.4765625</v>
       </c>
       <c r="C175" t="n">
         <v>135.1199951171875</v>
@@ -5061,7 +5061,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>147.4045562744141</v>
+        <v>147.404541015625</v>
       </c>
       <c r="C177" t="n">
         <v>164.6900024414062</v>
@@ -5090,7 +5090,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>148.4517517089844</v>
+        <v>148.4517364501953</v>
       </c>
       <c r="C178" t="n">
         <v>165.8600006103516</v>
@@ -5119,7 +5119,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>141.99267578125</v>
+        <v>141.9926910400391</v>
       </c>
       <c r="C179" t="n">
         <v>158.1000061035156</v>
@@ -5148,7 +5148,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>139.9449920654297</v>
+        <v>139.9449768066406</v>
       </c>
       <c r="C180" t="n">
         <v>155.8200073242188</v>
@@ -5206,7 +5206,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>150.3778533935547</v>
+        <v>150.3778228759766</v>
       </c>
       <c r="C182" t="n">
         <v>166.8500061035156</v>
@@ -5235,7 +5235,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>143.9788208007812</v>
+        <v>143.9787750244141</v>
       </c>
       <c r="C183" t="n">
         <v>159.75</v>
@@ -5264,7 +5264,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>171.4045715332031</v>
+        <v>171.4046020507812</v>
       </c>
       <c r="C184" t="n">
         <v>190.1799926757812</v>
@@ -5293,7 +5293,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>177.3970489501953</v>
+        <v>177.3970642089844</v>
       </c>
       <c r="C185" t="n">
         <v>196.25</v>
@@ -5351,7 +5351,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>175.3360748291016</v>
+        <v>175.3361053466797</v>
       </c>
       <c r="C187" t="n">
         <v>193.9700012207031</v>
@@ -5380,7 +5380,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>174.9044036865234</v>
+        <v>174.9044189453125</v>
       </c>
       <c r="C188" t="n">
         <v>192.6900024414062</v>
@@ -5438,7 +5438,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>184.1356811523438</v>
+        <v>184.1357116699219</v>
       </c>
       <c r="C190" t="n">
         <v>202.8600006103516</v>
@@ -5467,7 +5467,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>213.0065460205078</v>
+        <v>213.0065612792969</v>
       </c>
       <c r="C191" t="n">
         <v>233.8200073242188</v>
@@ -5496,7 +5496,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>222.8178558349609</v>
+        <v>222.81787109375</v>
       </c>
       <c r="C192" t="n">
         <v>244.5899963378906</v>
@@ -5525,7 +5525,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>235.4714660644531</v>
+        <v>235.4714965820312</v>
       </c>
       <c r="C193" t="n">
         <v>258.4800109863281</v>
@@ -5554,7 +5554,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>216.9353637695312</v>
+        <v>216.9353790283203</v>
       </c>
       <c r="C194" t="n">
         <v>237.3500061035156</v>
@@ -5583,7 +5583,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>202.0464630126953</v>
+        <v>202.0464477539062</v>
       </c>
       <c r="C195" t="n">
         <v>221.0599975585938</v>
@@ -5612,7 +5612,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>184.7994995117188</v>
+        <v>184.7994842529297</v>
       </c>
       <c r="C196" t="n">
         <v>202.1900024414062</v>
@@ -5641,7 +5641,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>181.454345703125</v>
+        <v>181.4543304443359</v>
       </c>
       <c r="C197" t="n">
         <v>197.7299957275391</v>
@@ -5670,7 +5670,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>179.2243499755859</v>
+        <v>179.2243347167969</v>
       </c>
       <c r="C198" t="n">
         <v>195.3000030517578</v>
@@ -5699,7 +5699,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>160.2924346923828</v>
+        <v>160.2924499511719</v>
       </c>
       <c r="C199" t="n">
         <v>174.6699981689453</v>
@@ -5728,7 +5728,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>176.7636413574219</v>
+        <v>176.7636260986328</v>
       </c>
       <c r="C200" t="n">
         <v>191.5299987792969</v>
@@ -5757,7 +5757,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>179.1724548339844</v>
+        <v>179.1724243164062</v>
       </c>
       <c r="C201" t="n">
         <v>194.1399993896484</v>
@@ -5786,7 +5786,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>173.3304290771484</v>
+        <v>173.3304443359375</v>
       </c>
       <c r="C202" t="n">
         <v>187.8099975585938</v>
@@ -5844,7 +5844,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>197.2300872802734</v>
+        <v>197.2300415039062</v>
       </c>
       <c r="C204" t="n">
         <v>212.5500030517578</v>
@@ -5873,7 +5873,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>184.8793792724609</v>
+        <v>184.8794250488281</v>
       </c>
       <c r="C205" t="n">
         <v>199.2400054931641</v>
@@ -5902,7 +5902,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>194.2342834472656</v>
+        <v>194.2343444824219</v>
       </c>
       <c r="C206" t="n">
         <v>208.25</v>
@@ -5931,7 +5931,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>191.902587890625</v>
+        <v>191.9025726318359</v>
       </c>
       <c r="C207" t="n">
         <v>205.75</v>
@@ -5960,7 +5960,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>186.5115814208984</v>
+        <v>186.5115966796875</v>
       </c>
       <c r="C208" t="n">
         <v>199.9700012207031</v>
@@ -6018,7 +6018,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>188.5315399169922</v>
+        <v>188.5315246582031</v>
       </c>
       <c r="C210" t="n">
         <v>201.1300048828125</v>
@@ -6047,7 +6047,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>211.5625</v>
+        <v>211.5624694824219</v>
       </c>
       <c r="C211" t="n">
         <v>225.6999969482422</v>
@@ -6076,7 +6076,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>220.6328277587891</v>
+        <v>220.6328430175781</v>
       </c>
       <c r="C212" t="n">
         <v>234.2700042724609</v>
@@ -6192,7 +6192,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>188.3557281494141</v>
+        <v>188.355712890625</v>
       </c>
       <c r="C216" t="n">
         <v>198.8300018310547</v>
@@ -6221,7 +6221,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>210.8261260986328</v>
+        <v>210.8261566162109</v>
       </c>
       <c r="C217" t="n">
         <v>222.5500030517578</v>
@@ -6279,7 +6279,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>229.1380310058594</v>
+        <v>229.1380004882812</v>
       </c>
       <c r="C219" t="n">
         <v>240.6699981689453</v>
@@ -6308,7 +6308,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>242.5242919921875</v>
+        <v>242.5242767333984</v>
       </c>
       <c r="C220" t="n">
         <v>254.7299957275391</v>
@@ -6337,7 +6337,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>218.1031494140625</v>
+        <v>218.1031646728516</v>
       </c>
       <c r="C221" t="n">
         <v>227.9900054931641</v>
@@ -6424,7 +6424,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>236.0022430419922</v>
+        <v>236.0022583007812</v>
       </c>
       <c r="C224" t="n">
         <v>245.5099945068359</v>
@@ -6453,7 +6453,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>238.87646484375</v>
+        <v>238.8764495849609</v>
       </c>
       <c r="C225" t="n">
         <v>248.5</v>
@@ -6482,7 +6482,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>260.3609008789062</v>
+        <v>260.3609313964844</v>
       </c>
       <c r="C226" t="n">
         <v>270.8500061035156</v>
@@ -6511,7 +6511,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>252.7580261230469</v>
+        <v>252.7580108642578</v>
       </c>
       <c r="C227" t="n">
         <v>261.8299865722656</v>
@@ -6540,7 +6540,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>262.9906921386719</v>
+        <v>262.99072265625</v>
       </c>
       <c r="C228" t="n">
         <v>272.4299926757812</v>
@@ -6598,7 +6598,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>252.1268768310547</v>
+        <v>252.1268920898438</v>
       </c>
       <c r="C230" t="n">
         <v>260.0400085449219</v>
@@ -6627,7 +6627,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>241.0737762451172</v>
+        <v>241.0737915039062</v>
       </c>
       <c r="C231" t="n">
         <v>248.6399993896484</v>
@@ -6685,7 +6685,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>217.9008331298828</v>
+        <v>217.9008178710938</v>
       </c>
       <c r="C233" t="n">
         <v>223.5599975585938</v>
@@ -6714,7 +6714,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>220.0158843994141</v>
+        <v>220.0159149169922</v>
       </c>
       <c r="C234" t="n">
         <v>225.7299957275391</v>
@@ -6743,7 +6743,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>216.2536163330078</v>
+        <v>216.2536010742188</v>
       </c>
       <c r="C235" t="n">
         <v>221.8699951171875</v>
@@ -6801,7 +6801,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>252.8652191162109</v>
+        <v>252.8652496337891</v>
       </c>
       <c r="C237" t="n">
         <v>258.0599975585938</v>
@@ -6830,7 +6830,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>246.2511138916016</v>
+        <v>246.2511291503906</v>
       </c>
       <c r="C238" t="n">
         <v>251.3099975585938</v>
@@ -6888,7 +6888,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>238.7670440673828</v>
+        <v>238.7670593261719</v>
       </c>
       <c r="C240" t="n">
         <v>242.4799957275391</v>
